--- a/xls/MatrizDeConfusao.xlsx
+++ b/xls/MatrizDeConfusao.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="EstaPasta_de_trabalho" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2025/xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2026/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="11_AC8E5BFECF7AE82350DD8549A1A28A4A78DA7722" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8BAD26B-6BA8-4A84-BBC1-93FDD9A54BD6}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="11_AC8E5BFECF7AE82350DD8549A1A28A4A78DA7722" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60E3AFCB-D694-4EF8-B08E-74F29A2EDFED}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MatrizConfusão" sheetId="22" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>REFERÊNCIA</t>
   </si>
@@ -103,6 +103,12 @@
   </si>
   <si>
     <t>Matriz Não Enviesada</t>
+  </si>
+  <si>
+    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2026</t>
+  </si>
+  <si>
+    <t>#https://cdrenno.github.io/Estatistica/</t>
   </si>
 </sst>
 </file>
@@ -311,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -360,6 +366,33 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -374,36 +407,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -621,10 +624,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -914,15 +913,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:P27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:P31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="13" max="14" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>16</v>
       </c>
@@ -930,18 +929,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="D2" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D2" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
       <c r="K2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D3" s="6">
         <v>1</v>
       </c>
@@ -961,8 +960,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="22" t="s">
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="31" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="6">
@@ -980,11 +979,11 @@
       <c r="G4" s="5">
         <v>0</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="20">
         <f>SUM(D4:G4)</f>
         <v>33</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="20">
         <v>1000</v>
       </c>
       <c r="K4" t="s">
@@ -994,8 +993,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B5" s="23"/>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B5" s="32"/>
       <c r="C5" s="8">
         <v>2</v>
       </c>
@@ -1011,11 +1010,11 @@
       <c r="G5" s="1">
         <v>4</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="21">
         <f>SUM(D5:G5)</f>
         <v>46</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="21">
         <v>950</v>
       </c>
       <c r="K5" t="s">
@@ -1025,8 +1024,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B6" s="23"/>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B6" s="32"/>
       <c r="C6" s="8">
         <v>3</v>
       </c>
@@ -1042,11 +1041,11 @@
       <c r="G6" s="1">
         <v>8</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="21">
         <f>SUM(D6:G6)</f>
         <v>69</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="21">
         <v>300</v>
       </c>
       <c r="K6" t="s">
@@ -1056,8 +1055,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B7" s="24"/>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B7" s="33"/>
       <c r="C7" s="8">
         <v>4</v>
       </c>
@@ -1073,11 +1072,11 @@
       <c r="G7" s="1">
         <v>52</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="21">
         <f>SUM(D7:G7)</f>
         <v>52</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="23">
         <v>250</v>
       </c>
       <c r="K7" t="s">
@@ -1087,7 +1086,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C8" s="3" t="s">
         <v>4</v>
       </c>
@@ -1112,7 +1111,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C9" s="3" t="s">
         <v>6</v>
       </c>
@@ -1128,7 +1127,7 @@
         <f t="array" ref="F9">SUM($I4:$I7*F4:F7/$H4:$H7)</f>
         <v>251.08695652173913</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="22">
         <f t="array" ref="G9">SUM($I4:$I7*G4:G7/$H4:$H7)</f>
         <v>367.39130434782606</v>
       </c>
@@ -1137,7 +1136,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>22</v>
       </c>
@@ -1145,21 +1144,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="D12" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="M12" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="N12" s="21"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D12" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="M12" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D13" s="6">
         <v>1</v>
       </c>
@@ -1188,8 +1187,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B14" s="22" t="s">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B14" s="31" t="s">
         <v>1</v>
       </c>
       <c r="C14" s="6">
@@ -1211,11 +1210,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="20">
         <f>SUM(D14:G14)</f>
         <v>0.40000000000000008</v>
       </c>
-      <c r="K14" s="22" t="s">
+      <c r="K14" s="31" t="s">
         <v>1</v>
       </c>
       <c r="L14" s="6">
@@ -1232,13 +1231,13 @@
         <f>$I4*$I4*(F4/$H4)*(1-F4/$H4)/($H4-1)</f>
         <v>0</v>
       </c>
-      <c r="P14" s="29">
+      <c r="P14" s="24">
         <f>$I4*$I4*(G4/$H4)*(1-G4/$H4)/($H4-1)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B15" s="23"/>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B15" s="32"/>
       <c r="C15" s="8">
         <v>2</v>
       </c>
@@ -1258,11 +1257,11 @@
         <f t="shared" si="0"/>
         <v>3.3043478260869563E-2</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="21">
         <f>SUM(D15:G15)</f>
         <v>0.38</v>
       </c>
-      <c r="K15" s="23"/>
+      <c r="K15" s="32"/>
       <c r="L15" s="8">
         <v>2</v>
       </c>
@@ -1270,20 +1269,20 @@
         <f>$I5*$I5*(D5/$H5)*(1-D5/$H5)/($H5-1)</f>
         <v>2274.7321991178324</v>
       </c>
-      <c r="N15" s="30">
-        <v>0</v>
-      </c>
-      <c r="O15" s="30">
+      <c r="N15" s="15">
+        <v>0</v>
+      </c>
+      <c r="O15" s="15">
         <f>$I5*$I5*(F5/$H5)*(1-F5/$H5)/($H5-1)</f>
         <v>426.51228733459357</v>
       </c>
-      <c r="P15" s="31">
+      <c r="P15" s="25">
         <f>$I5*$I5*(G5/$H5)*(1-G5/$H5)/($H5-1)</f>
         <v>1592.3125393824826</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B16" s="23"/>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B16" s="32"/>
       <c r="C16" s="8">
         <v>3</v>
       </c>
@@ -1303,11 +1302,11 @@
         <f t="shared" si="0"/>
         <v>1.391304347826087E-2</v>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="21">
         <f>SUM(D16:G16)</f>
         <v>0.12000000000000001</v>
       </c>
-      <c r="K16" s="23"/>
+      <c r="K16" s="32"/>
       <c r="L16" s="8">
         <v>3</v>
       </c>
@@ -1315,20 +1314,20 @@
         <f>$I6*$I6*(D6/$H6)*(1-D6/$H6)/($H6-1)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="30">
+      <c r="N16" s="15">
         <f>$I6*$I6*(E6/$H6)*(1-E6/$H6)/($H6-1)</f>
         <v>135.66106972089403</v>
       </c>
-      <c r="O16" s="30">
-        <v>0</v>
-      </c>
-      <c r="P16" s="31">
+      <c r="O16" s="15">
+        <v>0</v>
+      </c>
+      <c r="P16" s="25">
         <f>$I6*$I6*(G6/$H6)*(1-G6/$H6)/($H6-1)</f>
         <v>135.66106972089403</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B17" s="24"/>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B17" s="33"/>
       <c r="C17" s="8">
         <v>4</v>
       </c>
@@ -1348,31 +1347,31 @@
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="21">
         <f>SUM(D17:G17)</f>
         <v>0.1</v>
       </c>
-      <c r="K17" s="24"/>
+      <c r="K17" s="33"/>
       <c r="L17" s="8">
         <v>4</v>
       </c>
-      <c r="M17" s="32">
+      <c r="M17" s="26">
         <f>$I7*$I7*(D7/$H7)*(1-D7/$H7)/($H7-1)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="33">
+      <c r="N17" s="27">
         <f>$I7*$I7*(E7/$H7)*(1-E7/$H7)/($H7-1)</f>
         <v>0</v>
       </c>
-      <c r="O17" s="33">
+      <c r="O17" s="27">
         <f>$I7*$I7*(F7/$H7)*(1-F7/$H7)/($H7-1)</f>
         <v>0</v>
       </c>
-      <c r="P17" s="34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="P17" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1397,7 +1396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C20" s="9" t="s">
         <v>10</v>
       </c>
@@ -1406,7 +1405,7 @@
         <v>0.80857707509881427</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C21" s="9" t="s">
         <v>15</v>
       </c>
@@ -1415,7 +1414,7 @@
         <v>1.3653678092858065E-3</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D23" s="1" t="s">
         <v>9</v>
       </c>
@@ -1429,7 +1428,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C24" s="6">
         <v>1</v>
       </c>
@@ -1450,7 +1449,7 @@
         <v>2.0135102333084364E-3</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C25" s="8">
         <v>2</v>
       </c>
@@ -1471,7 +1470,7 @@
         <v>3.4110679283624263E-3</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C26" s="8">
         <v>3</v>
       </c>
@@ -1492,7 +1491,7 @@
         <v>5.7208478280537664E-3</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C27" s="8">
         <v>4</v>
       </c>
@@ -1511,6 +1510,16 @@
       <c r="G27" s="17">
         <f>((G9^2)*((1-F27)^2)*D27*(1-D27)/(G8-1)+(F27^2)*SUM(P14:P17))/(G9^2)</f>
         <v>5.9279104034761256E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
